--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>06/23 11:41:10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>49000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>5764.71</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5764.71</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5764.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -75,183 +75,225 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06/23 11:41:19</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>11764.71</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>06/23 11:41:10</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>49000</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>5764.71</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>49000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5764.71</t>
+          <t>149000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17529.41</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>5764.71</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>17529.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -241,59 +241,86 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>06/23 11:41:31</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>149000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17529.41</t>
+          <t>149000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17529.41</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>17529.41</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>16641.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -244,83 +244,110 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>06/23 11:54:34</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>16641</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>06/23 11:41:31</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>888</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>149000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17529.41</t>
+          <t>149000</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>888</t>
+          <t>17529.41</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>17529</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>16641.41</t>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.41</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/23 11:41:19</t>
+          <t>06/23 18:37:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -117,237 +117,279 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06/23 11:41:19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>11764.71</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>06/23 11:41:10</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>49000</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>5764.71</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>时间</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>标记人</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>操作人</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>备注</t>
+          <t>下发</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/23 11:54:34</t>
+          <t>时间</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16641</t>
+          <t>金额</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t/>
+          <t>标记人</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t/>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>06/23 11:54:34</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>16641</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>06/23 11:41:31</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>888</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>149000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17529.41</t>
+          <t>469000</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17529</t>
+          <t>56083.63</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>17529</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>0.41</t>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>38554.63</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -286,12 +286,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06/23 11:54:34</t>
+          <t>06/23 19:48:23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16641</t>
+          <t>38554</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -301,7 +301,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -313,83 +313,110 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>06/23 11:54:34</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>16641</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>06/23 11:41:31</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>888</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>469000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>56083.63</t>
+          <t>469000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17529</t>
+          <t>56083.63</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>56083</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>38554.63</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.63</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -72,144 +72,186 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>代付</t>
-        </is>
-      </c>
-    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>06/24 12:44:14</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>300000</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>34883.72</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>白金林</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>代付</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>费率</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>汇率</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>结算</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>下发</t>
-        </is>
-      </c>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>下发</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>金额</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>标记人</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>操作人</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>0</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34883.72</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>34883.72</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>06/24 12:44:29</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>34883.72</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34883.72</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>688</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>34883.72</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>34195.72</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -202,83 +202,110 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>06/24 14:09:55</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>34195</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>06/24 12:44:29</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>688</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>tiantiananxin</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>300000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>34883.72</t>
+          <t>300000</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>34883.72</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>34883</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>34195.72</t>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0.72</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/24 12:44:14</t>
+          <t>06/25 13:06:41</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>320000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,17 +90,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>34883.72</t>
+          <t>38554.22</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>白金林</t>
+          <t/>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -199,113 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>06/24 14:09:55</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>34195</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06/24 12:44:29</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>688</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>320000</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>应下发</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>38554.22</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>34883.72</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>已下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>34883</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>0.72</t>
+          <t>38554.22</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>06/25 14:54:20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>38554</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>320000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>320000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38554.22</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>38554</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>38554.22</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.22</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/25 13:06:41</t>
+          <t>06/29 12:24:56</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>200000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>24096.39</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>06/25 14:54:20</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>38554</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>200000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>320000</t>
+          <t>24096.39</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>38554.22</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>38554</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.22</t>
+          <t>24096.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>06/29 13:45:30</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>24096</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>200000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>200000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24096.39</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>24096</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>24096.39</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.39</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/29 12:24:56</t>
+          <t>06/30 18:55:09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>280000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -95,7 +95,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>33734.94</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>tiantiananxin</t>
+          <t>jxxiaomei521</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>06/29 13:45:30</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>24096</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>280000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>200000</t>
+          <t>33734.94</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24096.39</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24096</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.39</t>
+          <t>33734.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>06/30 20:04:43</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>33734</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>280000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>280000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33734.94</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>33734</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>33734.94</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.94</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06/30 18:55:09</t>
+          <t>07/01 11:40:21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>100000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>11764.71</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>06/30 20:04:43</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>33734</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>280000</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>33734.94</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>33734</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.94</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/01 16:31:08</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jxxiaomei521</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>100000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>100000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11764.71</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>11764.71</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.71</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/01 11:40:21</t>
+          <t>07/13 10:43:40</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>600000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>73170.73</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -105,7 +105,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>jxxiaomei521</t>
+          <t>tiantiananxin</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/01 16:31:08</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>11764</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>jxxiaomei521</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>600000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>73170.73</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11764.71</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11764</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.71</t>
+          <t>73170.73</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/13 15:19:30</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>73170</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>600000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>73170.73</t>
+          <t>600000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>73170.73</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>73170</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>73170.73</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.73</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -75,12 +75,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07/13 10:43:40</t>
+          <t>07/16 12:24:53</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>220000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -90,12 +90,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>73170.73</t>
+          <t>25581.4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -199,86 +199,59 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07/13 15:19:30</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>73170</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tiantiananxin</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>总计</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>总入款</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>220000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>总入款</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>600000</t>
+          <t>25581.4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>已下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>73170.73</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>未下发</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>73170</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>未下发</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>0.73</t>
+          <t>25581.4</t>
         </is>
       </c>
     </row>

--- a/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
+++ b/bills/JXZFSP/-5155950658/c7b33e3a7a4996f8e972f8265229dd2edb672edc4fd9664e263653f9488f271a/bill-current.xlsx
@@ -199,59 +199,86 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07/16 14:45:05</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>25581</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tiantiananxin</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>总入款</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>220000</t>
+          <t>总计</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>应下发</t>
+          <t>总入款</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>25581.4</t>
+          <t>220000</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>已下发</t>
+          <t>应下发</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25581.4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>已下发</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>25581</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未下发</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>25581.4</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.4</t>
         </is>
       </c>
     </row>
